--- a/商場年業績表_含成長率.xlsx
+++ b/商場年業績表_含成長率.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wowprime0-my.sharepoint.com/personal/ian_chiang_wowprime_com/Documents/data/開發部數據管理/百貨商場/quadrant_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_CFD6D139B92B66C9D42A8B5AE06BD3A5E15FCDBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EABD9D33-C477-403F-BF1F-6F8EB93086C5}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_CFD6D139B92B66C9D42A8B5AE06BD3A5E15FCDBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1CF984B-7DF0-43C6-8802-1DDB9BCB3DAF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="9120" yWindow="2760" windowWidth="14895" windowHeight="12720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="地區型商場" sheetId="1" r:id="rId1"/>
@@ -4804,7 +4804,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilteredData" displayName="FilteredData" ref="A1:I103">
-  <autoFilter ref="A1:I103" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A1:I103" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="greaterThanOrEqual" val="100"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="體系"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="商場名稱"/>
@@ -29269,7 +29275,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>23</v>
       </c>
@@ -29298,7 +29304,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>23</v>
       </c>
@@ -29327,7 +29333,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>23</v>
       </c>
@@ -29356,7 +29362,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>23</v>
       </c>
@@ -29385,7 +29391,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
         <v>107</v>
       </c>
@@ -29414,7 +29420,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
         <v>107</v>
       </c>
@@ -29443,7 +29449,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
         <v>23</v>
       </c>
@@ -29470,7 +29476,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
         <v>107</v>
       </c>
@@ -29499,7 +29505,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
         <v>107</v>
       </c>
@@ -29557,7 +29563,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>173</v>
       </c>
@@ -29586,7 +29592,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>173</v>
       </c>
@@ -29613,7 +29619,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
         <v>173</v>
       </c>
@@ -29640,7 +29646,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
         <v>107</v>
       </c>
@@ -29669,7 +29675,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
         <v>107</v>
       </c>
@@ -29698,7 +29704,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
         <v>107</v>
       </c>
@@ -29756,7 +29762,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>214</v>
       </c>
@@ -29785,7 +29791,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
         <v>214</v>
       </c>
@@ -29814,7 +29820,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
         <v>23</v>
       </c>
@@ -29843,7 +29849,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
         <v>214</v>
       </c>
@@ -29872,7 +29878,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
         <v>221</v>
       </c>
@@ -29901,7 +29907,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
         <v>214</v>
       </c>
@@ -29930,7 +29936,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
         <v>23</v>
       </c>
@@ -29959,7 +29965,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
         <v>23</v>
       </c>
@@ -29988,7 +29994,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
         <v>397</v>
       </c>
@@ -30017,7 +30023,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
         <v>214</v>
       </c>
@@ -30075,7 +30081,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
         <v>23</v>
       </c>
@@ -30104,7 +30110,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
         <v>23</v>
       </c>
@@ -30133,7 +30139,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
         <v>214</v>
       </c>
@@ -30162,7 +30168,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
         <v>23</v>
       </c>
@@ -30191,7 +30197,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="27" t="s">
         <v>107</v>
       </c>
@@ -30220,7 +30226,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
         <v>23</v>
       </c>
@@ -30247,7 +30253,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="27" t="s">
         <v>23</v>
       </c>
@@ -30276,7 +30282,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
         <v>23</v>
       </c>
@@ -30305,7 +30311,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
         <v>23</v>
       </c>
@@ -30334,7 +30340,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
         <v>23</v>
       </c>
@@ -30363,7 +30369,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="27" t="s">
         <v>23</v>
       </c>
@@ -30392,7 +30398,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
         <v>23</v>
       </c>
@@ -30419,7 +30425,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="27" t="s">
         <v>397</v>
       </c>
@@ -30448,7 +30454,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="27" t="s">
         <v>23</v>
       </c>
@@ -30477,7 +30483,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="27" t="s">
         <v>221</v>
       </c>
@@ -30506,7 +30512,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
         <v>397</v>
       </c>
@@ -30535,7 +30541,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="27" t="s">
         <v>221</v>
       </c>
@@ -30593,7 +30599,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
         <v>23</v>
       </c>
@@ -30651,7 +30657,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="27" t="s">
         <v>221</v>
       </c>
@@ -30680,7 +30686,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
         <v>23</v>
       </c>
@@ -30709,7 +30715,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="27" t="s">
         <v>214</v>
       </c>
@@ -30767,7 +30773,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="27" t="s">
         <v>23</v>
       </c>
@@ -30794,7 +30800,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
         <v>23</v>
       </c>
@@ -30821,7 +30827,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="27" t="s">
         <v>23</v>
       </c>
@@ -30908,7 +30914,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
         <v>23</v>
       </c>
@@ -30937,7 +30943,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="27" t="s">
         <v>397</v>
       </c>
@@ -30966,7 +30972,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
         <v>23</v>
       </c>
@@ -30995,7 +31001,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
         <v>214</v>
       </c>
@@ -31024,7 +31030,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
         <v>397</v>
       </c>
@@ -31053,7 +31059,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="27" t="s">
         <v>23</v>
       </c>
@@ -31111,7 +31117,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="27" t="s">
         <v>996</v>
       </c>
@@ -31140,7 +31146,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="27" t="s">
         <v>1001</v>
       </c>
@@ -31198,7 +31204,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="27" t="s">
         <v>996</v>
       </c>
@@ -31227,7 +31233,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="27" t="s">
         <v>996</v>
       </c>
@@ -31256,7 +31262,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="27" t="s">
         <v>996</v>
       </c>
@@ -31285,7 +31291,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="27" t="s">
         <v>996</v>
       </c>
@@ -31314,7 +31320,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
         <v>996</v>
       </c>
@@ -31343,7 +31349,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="27" t="s">
         <v>996</v>
       </c>
@@ -31372,7 +31378,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
         <v>996</v>
       </c>
@@ -31401,7 +31407,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="27" t="s">
         <v>996</v>
       </c>
@@ -31430,7 +31436,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="27" t="s">
         <v>996</v>
       </c>
@@ -31515,7 +31521,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="27" t="s">
         <v>996</v>
       </c>
@@ -31544,7 +31550,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="27" t="s">
         <v>996</v>
       </c>
@@ -31573,7 +31579,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="27" t="s">
         <v>992</v>
       </c>
@@ -31602,7 +31608,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
         <v>996</v>
       </c>
@@ -31658,7 +31664,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
         <v>996</v>
       </c>
@@ -31687,7 +31693,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="27" t="s">
         <v>992</v>
       </c>
@@ -31716,7 +31722,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
         <v>1001</v>
       </c>
@@ -31745,7 +31751,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="27" t="s">
         <v>1078</v>
       </c>
@@ -31774,7 +31780,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
         <v>996</v>
       </c>
@@ -31832,7 +31838,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
         <v>992</v>
       </c>
@@ -31861,7 +31867,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="27" t="s">
         <v>1001</v>
       </c>
@@ -31890,7 +31896,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
         <v>996</v>
       </c>
@@ -31919,7 +31925,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="27" t="s">
         <v>1078</v>
       </c>
@@ -31948,7 +31954,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
         <v>992</v>
       </c>
@@ -31977,7 +31983,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="27" t="s">
         <v>992</v>
       </c>
@@ -32006,7 +32012,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
         <v>992</v>
       </c>
@@ -32035,7 +32041,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="27" t="s">
         <v>992</v>
       </c>
@@ -32064,7 +32070,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
         <v>992</v>
       </c>
@@ -32093,7 +32099,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="27" t="s">
         <v>996</v>
       </c>
@@ -32122,7 +32128,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="27" t="s">
         <v>992</v>
       </c>
@@ -32151,7 +32157,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="27" t="s">
         <v>996</v>
       </c>
@@ -32180,7 +32186,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="27" t="s">
         <v>1001</v>
       </c>
